--- a/data/03_03_2025_TMT.xlsx
+++ b/data/03_03_2025_TMT.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="25">
   <si>
     <t>Date</t>
   </si>
@@ -82,6 +82,24 @@
   <si>
     <t>03/03/2025</t>
   </si>
+  <si>
+    <t>04/03/2025</t>
+  </si>
+  <si>
+    <t>05/03/2025</t>
+  </si>
+  <si>
+    <t>06/03/2025</t>
+  </si>
+  <si>
+    <t>07/03/2025</t>
+  </si>
+  <si>
+    <t>08/03/2025</t>
+  </si>
+  <si>
+    <t>09/03/2025</t>
+  </si>
 </sst>
 </file>
 
@@ -116,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -134,11 +152,48 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9" tint="-0.24994659260841701"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -427,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G240"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" style="4" customWidth="1"/>
@@ -2042,7 +2097,7 @@
         <v>9</v>
       </c>
       <c r="G67" s="3" t="str">
-        <f t="shared" ref="G67:G110" si="1">IF(OR(E67="Yes", F67="YES"), "YES", "NO")</f>
+        <f t="shared" ref="G67:G130" si="1">IF(OR(E67="Yes", F67="YES"), "YES", "NO")</f>
         <v>YES</v>
       </c>
     </row>
@@ -3078,15 +3133,3165 @@
         <v>NO</v>
       </c>
     </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B111" s="9">
+        <v>7.7083333333333337E-2</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D111" s="3">
+        <v>8</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G111" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B112" s="9">
+        <v>0.16041666666666668</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D112" s="3">
+        <v>8</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G112" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B113" s="9">
+        <v>0.30555555555555552</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D113" s="3">
+        <v>8</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G113" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B114" s="9">
+        <v>0.31944444444444448</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D114" s="3">
+        <v>10</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G114" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B115" s="9">
+        <v>0.34791666666666665</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D115" s="3">
+        <v>10</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G115" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B116" s="9">
+        <v>0.3756944444444445</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D116" s="3">
+        <v>10</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G116" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B117" s="9">
+        <v>0.38263888888888892</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D117" s="3">
+        <v>8</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G117" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B118" s="9">
+        <v>0.41041666666666665</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D118" s="3">
+        <v>8</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G118" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B119" s="9">
+        <v>0.44027777777777777</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D119" s="3">
+        <v>8</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G119" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B120" s="9">
+        <v>0.47291666666666665</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D120" s="3">
+        <v>8</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G120" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B121" s="9">
+        <v>0.48472222222222222</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D121" s="3">
+        <v>8</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G121" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B122" s="9">
+        <v>0.56388888888888888</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D122" s="3">
+        <v>8</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G122" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B123" s="9">
+        <v>0.57500000000000007</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D123" s="3">
+        <v>8</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G123" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B124" s="9">
+        <v>0.57708333333333328</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D124" s="3">
+        <v>8</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G124" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B125" s="9">
+        <v>0.70624999999999993</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D125" s="3">
+        <v>8</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G125" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B126" s="9">
+        <v>0.72083333333333333</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D126" s="3">
+        <v>8</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G126" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B127" s="9">
+        <v>0.7270833333333333</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D127" s="3">
+        <v>8</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G127" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B128" s="9">
+        <v>0.78680555555555554</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D128" s="3">
+        <v>8</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G128" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B129" s="9">
+        <v>0.8222222222222223</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D129" s="3">
+        <v>8</v>
+      </c>
+      <c r="E129" t="s">
+        <v>8</v>
+      </c>
+      <c r="F129" t="s">
+        <v>8</v>
+      </c>
+      <c r="G129" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A130" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B130" s="9">
+        <v>0.82986111111111116</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D130" s="3">
+        <v>8</v>
+      </c>
+      <c r="E130" t="s">
+        <v>9</v>
+      </c>
+      <c r="F130" t="s">
+        <v>9</v>
+      </c>
+      <c r="G130" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A131" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B131" s="9">
+        <v>0.83819444444444446</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D131" s="3">
+        <v>8</v>
+      </c>
+      <c r="E131" t="s">
+        <v>8</v>
+      </c>
+      <c r="F131" t="s">
+        <v>8</v>
+      </c>
+      <c r="G131" s="3" t="str">
+        <f t="shared" ref="G131:G164" si="2">IF(OR(E131="Yes", F131="YES"), "YES", "NO")</f>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A132" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B132" s="9">
+        <v>0.89930555555555547</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D132" s="3">
+        <v>8</v>
+      </c>
+      <c r="E132" t="s">
+        <v>9</v>
+      </c>
+      <c r="F132" t="s">
+        <v>9</v>
+      </c>
+      <c r="G132" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A133" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B133" s="9">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="C133" t="s">
+        <v>10</v>
+      </c>
+      <c r="D133">
+        <v>8</v>
+      </c>
+      <c r="E133" t="s">
+        <v>9</v>
+      </c>
+      <c r="F133" t="s">
+        <v>9</v>
+      </c>
+      <c r="G133" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A134" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B134" s="9">
+        <v>4.027777777777778E-2</v>
+      </c>
+      <c r="C134" t="s">
+        <v>7</v>
+      </c>
+      <c r="D134">
+        <v>8</v>
+      </c>
+      <c r="E134" t="s">
+        <v>9</v>
+      </c>
+      <c r="F134" t="s">
+        <v>9</v>
+      </c>
+      <c r="G134" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B135" s="9">
+        <v>7.0833333333333331E-2</v>
+      </c>
+      <c r="C135" t="s">
+        <v>7</v>
+      </c>
+      <c r="D135">
+        <v>8</v>
+      </c>
+      <c r="E135" t="s">
+        <v>9</v>
+      </c>
+      <c r="F135" t="s">
+        <v>9</v>
+      </c>
+      <c r="G135" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B136" s="9">
+        <v>0.15902777777777777</v>
+      </c>
+      <c r="C136" t="s">
+        <v>10</v>
+      </c>
+      <c r="D136">
+        <v>8</v>
+      </c>
+      <c r="E136" t="s">
+        <v>9</v>
+      </c>
+      <c r="F136" t="s">
+        <v>9</v>
+      </c>
+      <c r="G136" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B137" s="9">
+        <v>0.16805555555555554</v>
+      </c>
+      <c r="C137" t="s">
+        <v>7</v>
+      </c>
+      <c r="D137">
+        <v>8</v>
+      </c>
+      <c r="E137" t="s">
+        <v>8</v>
+      </c>
+      <c r="F137" t="s">
+        <v>9</v>
+      </c>
+      <c r="G137" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B138" s="9">
+        <v>0.19027777777777777</v>
+      </c>
+      <c r="C138" t="s">
+        <v>7</v>
+      </c>
+      <c r="D138">
+        <v>8</v>
+      </c>
+      <c r="E138" t="s">
+        <v>9</v>
+      </c>
+      <c r="F138" t="s">
+        <v>8</v>
+      </c>
+      <c r="G138" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B139" s="9">
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="C139" t="s">
+        <v>7</v>
+      </c>
+      <c r="D139">
+        <v>8</v>
+      </c>
+      <c r="E139" t="s">
+        <v>9</v>
+      </c>
+      <c r="F139" t="s">
+        <v>9</v>
+      </c>
+      <c r="G139" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B140" s="9">
+        <v>0.24444444444444446</v>
+      </c>
+      <c r="C140" t="s">
+        <v>11</v>
+      </c>
+      <c r="D140">
+        <v>10</v>
+      </c>
+      <c r="E140" t="s">
+        <v>9</v>
+      </c>
+      <c r="F140" t="s">
+        <v>8</v>
+      </c>
+      <c r="G140" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B141" s="9">
+        <v>0.33611111111111108</v>
+      </c>
+      <c r="C141" t="s">
+        <v>7</v>
+      </c>
+      <c r="D141">
+        <v>8</v>
+      </c>
+      <c r="E141" t="s">
+        <v>9</v>
+      </c>
+      <c r="F141" t="s">
+        <v>8</v>
+      </c>
+      <c r="G141" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B142" s="9">
+        <v>0.36458333333333331</v>
+      </c>
+      <c r="C142" t="s">
+        <v>10</v>
+      </c>
+      <c r="D142">
+        <v>8</v>
+      </c>
+      <c r="E142" t="s">
+        <v>8</v>
+      </c>
+      <c r="F142" t="s">
+        <v>8</v>
+      </c>
+      <c r="G142" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B143" s="9">
+        <v>0.39513888888888887</v>
+      </c>
+      <c r="C143" t="s">
+        <v>10</v>
+      </c>
+      <c r="D143">
+        <v>8</v>
+      </c>
+      <c r="E143" t="s">
+        <v>8</v>
+      </c>
+      <c r="F143" t="s">
+        <v>9</v>
+      </c>
+      <c r="G143" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A144" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B144" s="9">
+        <v>0.47013888888888888</v>
+      </c>
+      <c r="C144" t="s">
+        <v>11</v>
+      </c>
+      <c r="D144">
+        <v>10</v>
+      </c>
+      <c r="E144" t="s">
+        <v>8</v>
+      </c>
+      <c r="F144" t="s">
+        <v>9</v>
+      </c>
+      <c r="G144" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B145" s="9">
+        <v>0.55277777777777781</v>
+      </c>
+      <c r="C145" t="s">
+        <v>7</v>
+      </c>
+      <c r="D145">
+        <v>8</v>
+      </c>
+      <c r="E145" t="s">
+        <v>8</v>
+      </c>
+      <c r="F145" t="s">
+        <v>9</v>
+      </c>
+      <c r="G145" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A146" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B146" s="9">
+        <v>0.57847222222222217</v>
+      </c>
+      <c r="C146" t="s">
+        <v>10</v>
+      </c>
+      <c r="D146">
+        <v>8</v>
+      </c>
+      <c r="E146" t="s">
+        <v>8</v>
+      </c>
+      <c r="F146" t="s">
+        <v>9</v>
+      </c>
+      <c r="G146" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A147" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B147" s="9">
+        <v>0.65347222222222223</v>
+      </c>
+      <c r="C147" t="s">
+        <v>10</v>
+      </c>
+      <c r="D147">
+        <v>8</v>
+      </c>
+      <c r="E147" t="s">
+        <v>9</v>
+      </c>
+      <c r="F147" t="s">
+        <v>9</v>
+      </c>
+      <c r="G147" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A148" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B148" s="9">
+        <v>0.66805555555555562</v>
+      </c>
+      <c r="C148" t="s">
+        <v>7</v>
+      </c>
+      <c r="D148">
+        <v>8</v>
+      </c>
+      <c r="E148" t="s">
+        <v>9</v>
+      </c>
+      <c r="F148" t="s">
+        <v>9</v>
+      </c>
+      <c r="G148" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A149" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B149" s="9">
+        <v>0.7055555555555556</v>
+      </c>
+      <c r="C149" t="s">
+        <v>7</v>
+      </c>
+      <c r="D149">
+        <v>8</v>
+      </c>
+      <c r="E149" t="s">
+        <v>9</v>
+      </c>
+      <c r="F149" t="s">
+        <v>9</v>
+      </c>
+      <c r="G149" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B150" s="9">
+        <v>0.84375</v>
+      </c>
+      <c r="C150" t="s">
+        <v>7</v>
+      </c>
+      <c r="D150">
+        <v>8</v>
+      </c>
+      <c r="E150" t="s">
+        <v>8</v>
+      </c>
+      <c r="F150" t="s">
+        <v>9</v>
+      </c>
+      <c r="G150" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A151" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B151" s="9">
+        <v>0.92569444444444438</v>
+      </c>
+      <c r="C151" t="s">
+        <v>7</v>
+      </c>
+      <c r="D151">
+        <v>8</v>
+      </c>
+      <c r="E151" t="s">
+        <v>8</v>
+      </c>
+      <c r="F151" t="s">
+        <v>9</v>
+      </c>
+      <c r="G151" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B152" s="9">
+        <v>0.99375000000000002</v>
+      </c>
+      <c r="C152" t="s">
+        <v>7</v>
+      </c>
+      <c r="D152">
+        <v>8</v>
+      </c>
+      <c r="E152" t="s">
+        <v>9</v>
+      </c>
+      <c r="F152" t="s">
+        <v>9</v>
+      </c>
+      <c r="G152" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A153" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B153" s="9">
+        <v>5.0694444444444452E-2</v>
+      </c>
+      <c r="C153" t="s">
+        <v>7</v>
+      </c>
+      <c r="D153">
+        <v>8</v>
+      </c>
+      <c r="E153" t="s">
+        <v>9</v>
+      </c>
+      <c r="F153" t="s">
+        <v>9</v>
+      </c>
+      <c r="G153" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A154" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B154" s="9">
+        <v>8.6111111111111124E-2</v>
+      </c>
+      <c r="C154" t="s">
+        <v>7</v>
+      </c>
+      <c r="D154">
+        <v>8</v>
+      </c>
+      <c r="E154" t="s">
+        <v>9</v>
+      </c>
+      <c r="F154" t="s">
+        <v>9</v>
+      </c>
+      <c r="G154" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B155" s="9">
+        <v>0.13749999999999998</v>
+      </c>
+      <c r="C155" t="s">
+        <v>7</v>
+      </c>
+      <c r="D155">
+        <v>8</v>
+      </c>
+      <c r="E155" t="s">
+        <v>9</v>
+      </c>
+      <c r="F155" t="s">
+        <v>9</v>
+      </c>
+      <c r="G155" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A156" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B156" s="9">
+        <v>0.19027777777777777</v>
+      </c>
+      <c r="C156" t="s">
+        <v>7</v>
+      </c>
+      <c r="D156">
+        <v>8</v>
+      </c>
+      <c r="E156" t="s">
+        <v>9</v>
+      </c>
+      <c r="F156" t="s">
+        <v>9</v>
+      </c>
+      <c r="G156" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A157" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B157" s="9">
+        <v>0.31597222222222221</v>
+      </c>
+      <c r="C157" t="s">
+        <v>10</v>
+      </c>
+      <c r="D157">
+        <v>8</v>
+      </c>
+      <c r="E157" t="s">
+        <v>8</v>
+      </c>
+      <c r="F157" t="s">
+        <v>8</v>
+      </c>
+      <c r="G157" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A158" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B158" s="9">
+        <v>0.57013888888888886</v>
+      </c>
+      <c r="C158" t="s">
+        <v>7</v>
+      </c>
+      <c r="D158">
+        <v>8</v>
+      </c>
+      <c r="E158" t="s">
+        <v>9</v>
+      </c>
+      <c r="F158" t="s">
+        <v>8</v>
+      </c>
+      <c r="G158" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A159" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B159" s="9">
+        <v>0.57013888888888886</v>
+      </c>
+      <c r="C159" t="s">
+        <v>10</v>
+      </c>
+      <c r="D159">
+        <v>8</v>
+      </c>
+      <c r="E159" t="s">
+        <v>8</v>
+      </c>
+      <c r="F159" t="s">
+        <v>9</v>
+      </c>
+      <c r="G159" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A160" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B160" s="9">
+        <v>0.59236111111111112</v>
+      </c>
+      <c r="C160" t="s">
+        <v>11</v>
+      </c>
+      <c r="D160">
+        <v>8</v>
+      </c>
+      <c r="E160" t="s">
+        <v>9</v>
+      </c>
+      <c r="F160" t="s">
+        <v>9</v>
+      </c>
+      <c r="G160" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A161" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B161" s="9">
+        <v>0.62847222222222221</v>
+      </c>
+      <c r="C161" t="s">
+        <v>10</v>
+      </c>
+      <c r="D161">
+        <v>8</v>
+      </c>
+      <c r="E161" t="s">
+        <v>9</v>
+      </c>
+      <c r="F161" t="s">
+        <v>8</v>
+      </c>
+      <c r="G161" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A162" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B162" s="9">
+        <v>0.6479166666666667</v>
+      </c>
+      <c r="C162" t="s">
+        <v>7</v>
+      </c>
+      <c r="D162">
+        <v>8</v>
+      </c>
+      <c r="E162" t="s">
+        <v>9</v>
+      </c>
+      <c r="F162" t="s">
+        <v>9</v>
+      </c>
+      <c r="G162" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A163" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B163" s="9">
+        <v>0.7895833333333333</v>
+      </c>
+      <c r="C163" t="s">
+        <v>7</v>
+      </c>
+      <c r="D163">
+        <v>8</v>
+      </c>
+      <c r="E163" t="s">
+        <v>9</v>
+      </c>
+      <c r="F163" t="s">
+        <v>9</v>
+      </c>
+      <c r="G163" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A164" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B164" s="9">
+        <v>0.89374999999999993</v>
+      </c>
+      <c r="C164" t="s">
+        <v>10</v>
+      </c>
+      <c r="D164">
+        <v>8</v>
+      </c>
+      <c r="E164" t="s">
+        <v>8</v>
+      </c>
+      <c r="F164" t="s">
+        <v>8</v>
+      </c>
+      <c r="G164" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A165" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B165" s="9">
+        <v>0.9</v>
+      </c>
+      <c r="C165" t="s">
+        <v>7</v>
+      </c>
+      <c r="D165">
+        <v>8</v>
+      </c>
+      <c r="E165" t="s">
+        <v>9</v>
+      </c>
+      <c r="F165" t="s">
+        <v>9</v>
+      </c>
+      <c r="G165" s="3" t="str">
+        <f t="shared" ref="G165:G223" si="3">IF(OR(E165="Yes", F165="YES"), "YES", "NO")</f>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A166" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B166" s="9">
+        <v>0.9590277777777777</v>
+      </c>
+      <c r="C166" t="s">
+        <v>7</v>
+      </c>
+      <c r="D166">
+        <v>8</v>
+      </c>
+      <c r="E166" t="s">
+        <v>9</v>
+      </c>
+      <c r="F166" t="s">
+        <v>9</v>
+      </c>
+      <c r="G166" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A167" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B167" s="9">
+        <v>0.97291666666666676</v>
+      </c>
+      <c r="C167" t="s">
+        <v>7</v>
+      </c>
+      <c r="D167">
+        <v>8</v>
+      </c>
+      <c r="E167" t="s">
+        <v>9</v>
+      </c>
+      <c r="F167" t="s">
+        <v>9</v>
+      </c>
+      <c r="G167" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A168" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B168" s="9">
+        <v>0.98611111111111116</v>
+      </c>
+      <c r="C168" t="s">
+        <v>7</v>
+      </c>
+      <c r="D168">
+        <v>8</v>
+      </c>
+      <c r="E168" t="s">
+        <v>9</v>
+      </c>
+      <c r="F168" t="s">
+        <v>9</v>
+      </c>
+      <c r="G168" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A169" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B169" s="9">
+        <v>1.8055555555555557E-2</v>
+      </c>
+      <c r="C169" t="s">
+        <v>7</v>
+      </c>
+      <c r="D169">
+        <v>8</v>
+      </c>
+      <c r="E169" t="s">
+        <v>9</v>
+      </c>
+      <c r="F169" t="s">
+        <v>9</v>
+      </c>
+      <c r="G169" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A170" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B170" s="9">
+        <v>2.7083333333333334E-2</v>
+      </c>
+      <c r="C170" t="s">
+        <v>10</v>
+      </c>
+      <c r="D170">
+        <v>8</v>
+      </c>
+      <c r="E170" t="s">
+        <v>8</v>
+      </c>
+      <c r="F170" t="s">
+        <v>9</v>
+      </c>
+      <c r="G170" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A171" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B171" s="9">
+        <v>3.125E-2</v>
+      </c>
+      <c r="C171" t="s">
+        <v>7</v>
+      </c>
+      <c r="D171">
+        <v>8</v>
+      </c>
+      <c r="E171" t="s">
+        <v>9</v>
+      </c>
+      <c r="F171" t="s">
+        <v>9</v>
+      </c>
+      <c r="G171" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A172" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B172" s="9">
+        <v>4.9305555555555554E-2</v>
+      </c>
+      <c r="C172" t="s">
+        <v>7</v>
+      </c>
+      <c r="D172">
+        <v>8</v>
+      </c>
+      <c r="E172" t="s">
+        <v>9</v>
+      </c>
+      <c r="F172" t="s">
+        <v>9</v>
+      </c>
+      <c r="G172" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A173" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B173" s="9">
+        <v>8.1250000000000003E-2</v>
+      </c>
+      <c r="C173" t="s">
+        <v>7</v>
+      </c>
+      <c r="D173">
+        <v>8</v>
+      </c>
+      <c r="E173" t="s">
+        <v>9</v>
+      </c>
+      <c r="F173" t="s">
+        <v>9</v>
+      </c>
+      <c r="G173" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A174" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B174" s="9">
+        <v>0.12291666666666667</v>
+      </c>
+      <c r="C174" t="s">
+        <v>7</v>
+      </c>
+      <c r="D174">
+        <v>8</v>
+      </c>
+      <c r="E174" t="s">
+        <v>9</v>
+      </c>
+      <c r="F174" t="s">
+        <v>9</v>
+      </c>
+      <c r="G174" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A175" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B175" s="9">
+        <v>0.17013888888888887</v>
+      </c>
+      <c r="C175" t="s">
+        <v>10</v>
+      </c>
+      <c r="D175">
+        <v>8</v>
+      </c>
+      <c r="E175" t="s">
+        <v>8</v>
+      </c>
+      <c r="F175" t="s">
+        <v>8</v>
+      </c>
+      <c r="G175" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A176" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B176" s="9">
+        <v>0.17361111111111113</v>
+      </c>
+      <c r="C176" t="s">
+        <v>7</v>
+      </c>
+      <c r="D176">
+        <v>8</v>
+      </c>
+      <c r="E176" t="s">
+        <v>9</v>
+      </c>
+      <c r="F176" t="s">
+        <v>9</v>
+      </c>
+      <c r="G176" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A177" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B177" s="9">
+        <v>0.21875</v>
+      </c>
+      <c r="C177" t="s">
+        <v>10</v>
+      </c>
+      <c r="D177">
+        <v>8</v>
+      </c>
+      <c r="E177" t="s">
+        <v>8</v>
+      </c>
+      <c r="F177" t="s">
+        <v>9</v>
+      </c>
+      <c r="G177" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A178" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B178" s="9">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="C178" t="s">
+        <v>10</v>
+      </c>
+      <c r="D178">
+        <v>8</v>
+      </c>
+      <c r="E178" t="s">
+        <v>9</v>
+      </c>
+      <c r="F178" t="s">
+        <v>8</v>
+      </c>
+      <c r="G178" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A179" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B179" s="9">
+        <v>0.4055555555555555</v>
+      </c>
+      <c r="C179" t="s">
+        <v>7</v>
+      </c>
+      <c r="D179">
+        <v>8</v>
+      </c>
+      <c r="E179" t="s">
+        <v>9</v>
+      </c>
+      <c r="F179" t="s">
+        <v>9</v>
+      </c>
+      <c r="G179" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A180" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B180" s="9">
+        <v>0.5131944444444444</v>
+      </c>
+      <c r="C180" t="s">
+        <v>7</v>
+      </c>
+      <c r="D180">
+        <v>8</v>
+      </c>
+      <c r="E180" t="s">
+        <v>9</v>
+      </c>
+      <c r="F180" t="s">
+        <v>9</v>
+      </c>
+      <c r="G180" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A181" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B181" s="9">
+        <v>0.5395833333333333</v>
+      </c>
+      <c r="C181" t="s">
+        <v>7</v>
+      </c>
+      <c r="D181">
+        <v>8</v>
+      </c>
+      <c r="E181" t="s">
+        <v>9</v>
+      </c>
+      <c r="F181" t="s">
+        <v>9</v>
+      </c>
+      <c r="G181" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A182" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B182" s="9">
+        <v>0.61736111111111114</v>
+      </c>
+      <c r="C182" t="s">
+        <v>7</v>
+      </c>
+      <c r="D182">
+        <v>8</v>
+      </c>
+      <c r="E182" t="s">
+        <v>9</v>
+      </c>
+      <c r="F182" t="s">
+        <v>9</v>
+      </c>
+      <c r="G182" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A183" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B183" s="9">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="C183" t="s">
+        <v>7</v>
+      </c>
+      <c r="D183">
+        <v>8</v>
+      </c>
+      <c r="E183" t="s">
+        <v>9</v>
+      </c>
+      <c r="F183" t="s">
+        <v>9</v>
+      </c>
+      <c r="G183" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A184" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B184" s="9">
+        <v>0.65625</v>
+      </c>
+      <c r="C184" t="s">
+        <v>7</v>
+      </c>
+      <c r="D184">
+        <v>8</v>
+      </c>
+      <c r="E184" t="s">
+        <v>9</v>
+      </c>
+      <c r="F184" t="s">
+        <v>9</v>
+      </c>
+      <c r="G184" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A185" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B185" s="9">
+        <v>0.67638888888888893</v>
+      </c>
+      <c r="C185" t="s">
+        <v>7</v>
+      </c>
+      <c r="D185">
+        <v>8</v>
+      </c>
+      <c r="E185" t="s">
+        <v>9</v>
+      </c>
+      <c r="F185" t="s">
+        <v>9</v>
+      </c>
+      <c r="G185" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A186" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B186" s="9">
+        <v>0.71111111111111114</v>
+      </c>
+      <c r="C186" t="s">
+        <v>7</v>
+      </c>
+      <c r="D186">
+        <v>8</v>
+      </c>
+      <c r="E186" t="s">
+        <v>9</v>
+      </c>
+      <c r="F186" t="s">
+        <v>9</v>
+      </c>
+      <c r="G186" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A187" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B187" s="9">
+        <v>0.77361111111111114</v>
+      </c>
+      <c r="C187" t="s">
+        <v>7</v>
+      </c>
+      <c r="D187">
+        <v>8</v>
+      </c>
+      <c r="E187" t="s">
+        <v>9</v>
+      </c>
+      <c r="F187" t="s">
+        <v>9</v>
+      </c>
+      <c r="G187" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A188" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B188" s="9">
+        <v>0.79305555555555562</v>
+      </c>
+      <c r="C188" t="s">
+        <v>7</v>
+      </c>
+      <c r="D188">
+        <v>8</v>
+      </c>
+      <c r="E188" t="s">
+        <v>9</v>
+      </c>
+      <c r="F188" t="s">
+        <v>9</v>
+      </c>
+      <c r="G188" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A189" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B189" s="9">
+        <v>0.88541666666666663</v>
+      </c>
+      <c r="C189" t="s">
+        <v>7</v>
+      </c>
+      <c r="D189">
+        <v>8</v>
+      </c>
+      <c r="E189" t="s">
+        <v>9</v>
+      </c>
+      <c r="F189" t="s">
+        <v>9</v>
+      </c>
+      <c r="G189" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A190" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B190" s="9">
+        <v>0.90347222222222223</v>
+      </c>
+      <c r="C190" t="s">
+        <v>7</v>
+      </c>
+      <c r="D190">
+        <v>8</v>
+      </c>
+      <c r="E190" t="s">
+        <v>9</v>
+      </c>
+      <c r="F190" t="s">
+        <v>9</v>
+      </c>
+      <c r="G190" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A191" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B191" s="9">
+        <v>0.92499999999999993</v>
+      </c>
+      <c r="C191" t="s">
+        <v>7</v>
+      </c>
+      <c r="D191">
+        <v>8</v>
+      </c>
+      <c r="E191" t="s">
+        <v>9</v>
+      </c>
+      <c r="F191" t="s">
+        <v>8</v>
+      </c>
+      <c r="G191" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A192" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B192" s="9">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="C192" t="s">
+        <v>7</v>
+      </c>
+      <c r="D192">
+        <v>8</v>
+      </c>
+      <c r="E192" t="s">
+        <v>9</v>
+      </c>
+      <c r="F192" t="s">
+        <v>9</v>
+      </c>
+      <c r="G192" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A193" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B193" s="9">
+        <v>5.8333333333333327E-2</v>
+      </c>
+      <c r="C193" t="s">
+        <v>7</v>
+      </c>
+      <c r="D193">
+        <v>8</v>
+      </c>
+      <c r="E193" t="s">
+        <v>9</v>
+      </c>
+      <c r="F193" t="s">
+        <v>9</v>
+      </c>
+      <c r="G193" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A194" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B194" s="9">
+        <v>9.4444444444444442E-2</v>
+      </c>
+      <c r="C194" t="s">
+        <v>7</v>
+      </c>
+      <c r="D194">
+        <v>8</v>
+      </c>
+      <c r="E194" t="s">
+        <v>9</v>
+      </c>
+      <c r="F194" t="s">
+        <v>9</v>
+      </c>
+      <c r="G194" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A195" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B195" s="9">
+        <v>0.2722222222222222</v>
+      </c>
+      <c r="C195" t="s">
+        <v>7</v>
+      </c>
+      <c r="D195">
+        <v>8</v>
+      </c>
+      <c r="E195" t="s">
+        <v>9</v>
+      </c>
+      <c r="F195" t="s">
+        <v>9</v>
+      </c>
+      <c r="G195" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A196" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B196" s="9">
+        <v>0.30972222222222223</v>
+      </c>
+      <c r="C196" t="s">
+        <v>7</v>
+      </c>
+      <c r="D196">
+        <v>8</v>
+      </c>
+      <c r="E196" t="s">
+        <v>8</v>
+      </c>
+      <c r="F196" t="s">
+        <v>9</v>
+      </c>
+      <c r="G196" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A197" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B197" s="9">
+        <v>0.32291666666666669</v>
+      </c>
+      <c r="C197" t="s">
+        <v>10</v>
+      </c>
+      <c r="D197">
+        <v>8</v>
+      </c>
+      <c r="E197" t="s">
+        <v>9</v>
+      </c>
+      <c r="F197" t="s">
+        <v>9</v>
+      </c>
+      <c r="G197" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A198" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B198" s="9">
+        <v>0.40069444444444446</v>
+      </c>
+      <c r="C198" t="s">
+        <v>7</v>
+      </c>
+      <c r="D198">
+        <v>8</v>
+      </c>
+      <c r="E198" t="s">
+        <v>9</v>
+      </c>
+      <c r="F198" t="s">
+        <v>9</v>
+      </c>
+      <c r="G198" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A199" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B199" s="9">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="C199" t="s">
+        <v>7</v>
+      </c>
+      <c r="D199">
+        <v>8</v>
+      </c>
+      <c r="E199" t="s">
+        <v>9</v>
+      </c>
+      <c r="F199" t="s">
+        <v>9</v>
+      </c>
+      <c r="G199" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A200" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B200" s="9">
+        <v>0.60902777777777783</v>
+      </c>
+      <c r="C200" t="s">
+        <v>7</v>
+      </c>
+      <c r="D200">
+        <v>8</v>
+      </c>
+      <c r="E200" t="s">
+        <v>8</v>
+      </c>
+      <c r="F200" t="s">
+        <v>9</v>
+      </c>
+      <c r="G200" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A201" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B201" s="9">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="C201" t="s">
+        <v>10</v>
+      </c>
+      <c r="D201">
+        <v>8</v>
+      </c>
+      <c r="E201" t="s">
+        <v>8</v>
+      </c>
+      <c r="F201" t="s">
+        <v>9</v>
+      </c>
+      <c r="G201" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A202" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B202" s="9">
+        <v>0.65833333333333333</v>
+      </c>
+      <c r="C202" t="s">
+        <v>7</v>
+      </c>
+      <c r="D202">
+        <v>8</v>
+      </c>
+      <c r="E202" t="s">
+        <v>8</v>
+      </c>
+      <c r="F202" t="s">
+        <v>9</v>
+      </c>
+      <c r="G202" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A203" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B203" s="9">
+        <v>0.68402777777777779</v>
+      </c>
+      <c r="C203" t="s">
+        <v>7</v>
+      </c>
+      <c r="D203">
+        <v>8</v>
+      </c>
+      <c r="E203" t="s">
+        <v>8</v>
+      </c>
+      <c r="F203" t="s">
+        <v>9</v>
+      </c>
+      <c r="G203" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A204" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B204" s="9">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="C204" t="s">
+        <v>7</v>
+      </c>
+      <c r="D204">
+        <v>8</v>
+      </c>
+      <c r="E204" t="s">
+        <v>9</v>
+      </c>
+      <c r="F204" t="s">
+        <v>9</v>
+      </c>
+      <c r="G204" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A205" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B205" s="9">
+        <v>0.78541666666666676</v>
+      </c>
+      <c r="C205" t="s">
+        <v>7</v>
+      </c>
+      <c r="D205">
+        <v>8</v>
+      </c>
+      <c r="E205" t="s">
+        <v>9</v>
+      </c>
+      <c r="F205" t="s">
+        <v>9</v>
+      </c>
+      <c r="G205" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A206" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B206" s="9">
+        <v>0.81041666666666667</v>
+      </c>
+      <c r="C206" t="s">
+        <v>7</v>
+      </c>
+      <c r="D206">
+        <v>8</v>
+      </c>
+      <c r="E206" t="s">
+        <v>9</v>
+      </c>
+      <c r="F206" t="s">
+        <v>9</v>
+      </c>
+      <c r="G206" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A207" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B207" s="9">
+        <v>0.86736111111111114</v>
+      </c>
+      <c r="C207" t="s">
+        <v>11</v>
+      </c>
+      <c r="D207">
+        <v>10</v>
+      </c>
+      <c r="E207" t="s">
+        <v>9</v>
+      </c>
+      <c r="F207" t="s">
+        <v>9</v>
+      </c>
+      <c r="G207" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A208" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B208" s="9">
+        <v>0.88680555555555562</v>
+      </c>
+      <c r="C208" t="s">
+        <v>11</v>
+      </c>
+      <c r="D208">
+        <v>10</v>
+      </c>
+      <c r="E208" t="s">
+        <v>9</v>
+      </c>
+      <c r="F208" t="s">
+        <v>9</v>
+      </c>
+      <c r="G208" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A209" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B209" s="9">
+        <v>0.90972222222222221</v>
+      </c>
+      <c r="C209" t="s">
+        <v>7</v>
+      </c>
+      <c r="D209">
+        <v>8</v>
+      </c>
+      <c r="E209" t="s">
+        <v>9</v>
+      </c>
+      <c r="F209" t="s">
+        <v>9</v>
+      </c>
+      <c r="G209" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A210" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B210" s="9">
+        <v>1.6666666666666666E-2</v>
+      </c>
+      <c r="C210" t="s">
+        <v>7</v>
+      </c>
+      <c r="D210">
+        <v>8</v>
+      </c>
+      <c r="E210" t="s">
+        <v>9</v>
+      </c>
+      <c r="F210" t="s">
+        <v>9</v>
+      </c>
+      <c r="G210" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A211" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B211" s="9">
+        <v>5.1388888888888894E-2</v>
+      </c>
+      <c r="C211" t="s">
+        <v>10</v>
+      </c>
+      <c r="D211">
+        <v>8</v>
+      </c>
+      <c r="E211" t="s">
+        <v>9</v>
+      </c>
+      <c r="F211" t="s">
+        <v>9</v>
+      </c>
+      <c r="G211" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A212" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B212" s="9">
+        <v>5.347222222222222E-2</v>
+      </c>
+      <c r="C212" t="s">
+        <v>7</v>
+      </c>
+      <c r="D212">
+        <v>8</v>
+      </c>
+      <c r="E212" t="s">
+        <v>8</v>
+      </c>
+      <c r="F212" t="s">
+        <v>9</v>
+      </c>
+      <c r="G212" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A213" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B213" s="9">
+        <v>7.0833333333333331E-2</v>
+      </c>
+      <c r="C213" t="s">
+        <v>10</v>
+      </c>
+      <c r="D213">
+        <v>8</v>
+      </c>
+      <c r="E213" t="s">
+        <v>8</v>
+      </c>
+      <c r="F213" t="s">
+        <v>9</v>
+      </c>
+      <c r="G213" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A214" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B214" s="9">
+        <v>7.2916666666666671E-2</v>
+      </c>
+      <c r="C214" t="s">
+        <v>7</v>
+      </c>
+      <c r="D214">
+        <v>8</v>
+      </c>
+      <c r="E214" t="s">
+        <v>8</v>
+      </c>
+      <c r="F214" t="s">
+        <v>9</v>
+      </c>
+      <c r="G214" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A215" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B215" s="9">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="C215" t="s">
+        <v>10</v>
+      </c>
+      <c r="D215">
+        <v>8</v>
+      </c>
+      <c r="E215" t="s">
+        <v>9</v>
+      </c>
+      <c r="F215" t="s">
+        <v>8</v>
+      </c>
+      <c r="G215" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A216" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B216" s="9">
+        <v>0.10486111111111111</v>
+      </c>
+      <c r="C216" t="s">
+        <v>7</v>
+      </c>
+      <c r="D216">
+        <v>8</v>
+      </c>
+      <c r="E216" t="s">
+        <v>9</v>
+      </c>
+      <c r="F216" t="s">
+        <v>9</v>
+      </c>
+      <c r="G216" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A217" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B217" s="9">
+        <v>0.14097222222222222</v>
+      </c>
+      <c r="C217" t="s">
+        <v>7</v>
+      </c>
+      <c r="D217">
+        <v>8</v>
+      </c>
+      <c r="E217" t="s">
+        <v>9</v>
+      </c>
+      <c r="F217" t="s">
+        <v>8</v>
+      </c>
+      <c r="G217" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A218" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B218" s="9">
+        <v>0.15208333333333332</v>
+      </c>
+      <c r="C218" t="s">
+        <v>10</v>
+      </c>
+      <c r="D218">
+        <v>8</v>
+      </c>
+      <c r="E218" t="s">
+        <v>8</v>
+      </c>
+      <c r="F218" t="s">
+        <v>9</v>
+      </c>
+      <c r="G218" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A219" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B219" s="9">
+        <v>0.15555555555555556</v>
+      </c>
+      <c r="C219" t="s">
+        <v>7</v>
+      </c>
+      <c r="D219">
+        <v>8</v>
+      </c>
+      <c r="E219" t="s">
+        <v>9</v>
+      </c>
+      <c r="F219" t="s">
+        <v>9</v>
+      </c>
+      <c r="G219" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A220" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B220" s="9">
+        <v>0.18402777777777779</v>
+      </c>
+      <c r="C220" t="s">
+        <v>7</v>
+      </c>
+      <c r="D220">
+        <v>8</v>
+      </c>
+      <c r="E220" t="s">
+        <v>9</v>
+      </c>
+      <c r="F220" t="s">
+        <v>9</v>
+      </c>
+      <c r="G220" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A221" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B221" s="9">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="C221" t="s">
+        <v>7</v>
+      </c>
+      <c r="D221">
+        <v>8</v>
+      </c>
+      <c r="E221" t="s">
+        <v>9</v>
+      </c>
+      <c r="F221" t="s">
+        <v>9</v>
+      </c>
+      <c r="G221" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A222" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B222" s="9">
+        <v>0.27638888888888885</v>
+      </c>
+      <c r="C222" t="s">
+        <v>7</v>
+      </c>
+      <c r="D222">
+        <v>8</v>
+      </c>
+      <c r="E222" t="s">
+        <v>8</v>
+      </c>
+      <c r="F222" t="s">
+        <v>9</v>
+      </c>
+      <c r="G222" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A223" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B223" s="9">
+        <v>0.2902777777777778</v>
+      </c>
+      <c r="C223" t="s">
+        <v>7</v>
+      </c>
+      <c r="D223">
+        <v>8</v>
+      </c>
+      <c r="E223" t="s">
+        <v>8</v>
+      </c>
+      <c r="F223" t="s">
+        <v>8</v>
+      </c>
+      <c r="G223" s="3" t="str">
+        <f t="shared" si="3"/>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A224" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B224" s="9">
+        <v>0.31388888888888888</v>
+      </c>
+      <c r="C224" t="s">
+        <v>10</v>
+      </c>
+      <c r="D224">
+        <v>8</v>
+      </c>
+      <c r="E224" t="s">
+        <v>8</v>
+      </c>
+      <c r="F224" t="s">
+        <v>9</v>
+      </c>
+      <c r="G224" s="3" t="str">
+        <f>IF(OR(E224="Yes", F224="YES"), "YES", "NO")</f>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A225" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B225" s="9">
+        <v>0.34652777777777777</v>
+      </c>
+      <c r="C225" t="s">
+        <v>7</v>
+      </c>
+      <c r="D225">
+        <v>8</v>
+      </c>
+      <c r="E225" t="s">
+        <v>8</v>
+      </c>
+      <c r="F225" t="s">
+        <v>9</v>
+      </c>
+      <c r="G225" s="3" t="str">
+        <f>IF(OR(E225="Yes", F225="YES"), "YES", "NO")</f>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A226" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B226" s="9">
+        <v>0.35347222222222219</v>
+      </c>
+      <c r="C226" t="s">
+        <v>10</v>
+      </c>
+      <c r="D226">
+        <v>8</v>
+      </c>
+      <c r="E226" t="s">
+        <v>9</v>
+      </c>
+      <c r="F226" t="s">
+        <v>9</v>
+      </c>
+      <c r="G226" s="3" t="str">
+        <f>IF(OR(E226="Yes", F226="YES"), "YES", "NO")</f>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A227" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B227" s="9">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="C227" t="s">
+        <v>7</v>
+      </c>
+      <c r="D227">
+        <v>8</v>
+      </c>
+      <c r="E227" t="s">
+        <v>8</v>
+      </c>
+      <c r="F227" t="s">
+        <v>9</v>
+      </c>
+      <c r="G227" s="3" t="str">
+        <f>IF(OR(E227="Yes", F227="YES"), "YES", "NO")</f>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A228" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B228" s="9">
+        <v>0.41111111111111115</v>
+      </c>
+      <c r="C228" t="s">
+        <v>7</v>
+      </c>
+      <c r="D228">
+        <v>8</v>
+      </c>
+      <c r="E228" t="s">
+        <v>8</v>
+      </c>
+      <c r="F228" t="s">
+        <v>9</v>
+      </c>
+      <c r="G228" s="3" t="str">
+        <f>IF(OR(E228="Yes", F228="YES"), "YES", "NO")</f>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A229" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B229" s="9">
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="C229" t="s">
+        <v>7</v>
+      </c>
+      <c r="D229">
+        <v>8</v>
+      </c>
+      <c r="E229" t="s">
+        <v>8</v>
+      </c>
+      <c r="F229" t="s">
+        <v>9</v>
+      </c>
+      <c r="G229" s="3" t="str">
+        <f>IF(OR(E229="Yes", F229="YES"), "YES", "NO")</f>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A230" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B230" s="9">
+        <v>0.43888888888888888</v>
+      </c>
+      <c r="C230" t="s">
+        <v>10</v>
+      </c>
+      <c r="D230">
+        <v>8</v>
+      </c>
+      <c r="E230" t="s">
+        <v>8</v>
+      </c>
+      <c r="F230" t="s">
+        <v>9</v>
+      </c>
+      <c r="G230" s="3" t="str">
+        <f>IF(OR(E230="Yes", F230="YES"), "YES", "NO")</f>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A231" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B231" s="9">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C231" t="s">
+        <v>10</v>
+      </c>
+      <c r="D231">
+        <v>8</v>
+      </c>
+      <c r="E231" t="s">
+        <v>8</v>
+      </c>
+      <c r="F231" t="s">
+        <v>9</v>
+      </c>
+      <c r="G231" s="3" t="str">
+        <f>IF(OR(E231="Yes", F231="YES"), "YES", "NO")</f>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A232" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B232" s="9">
+        <v>0.55486111111111114</v>
+      </c>
+      <c r="C232" t="s">
+        <v>10</v>
+      </c>
+      <c r="D232">
+        <v>8</v>
+      </c>
+      <c r="E232" t="s">
+        <v>9</v>
+      </c>
+      <c r="F232" t="s">
+        <v>9</v>
+      </c>
+      <c r="G232" s="3" t="str">
+        <f>IF(OR(E232="Yes", F232="YES"), "YES", "NO")</f>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A233" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B233" s="9">
+        <v>0.55833333333333335</v>
+      </c>
+      <c r="C233" t="s">
+        <v>7</v>
+      </c>
+      <c r="D233">
+        <v>8</v>
+      </c>
+      <c r="E233" t="s">
+        <v>8</v>
+      </c>
+      <c r="F233" t="s">
+        <v>9</v>
+      </c>
+      <c r="G233" s="3" t="str">
+        <f>IF(OR(E233="Yes", F233="YES"), "YES", "NO")</f>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A234" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B234" s="9">
+        <v>0.63124999999999998</v>
+      </c>
+      <c r="C234" t="s">
+        <v>7</v>
+      </c>
+      <c r="D234">
+        <v>8</v>
+      </c>
+      <c r="E234" t="s">
+        <v>9</v>
+      </c>
+      <c r="F234" t="s">
+        <v>9</v>
+      </c>
+      <c r="G234" s="3" t="str">
+        <f>IF(OR(E234="Yes", F234="YES"), "YES", "NO")</f>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A235" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B235" s="9">
+        <v>0.64861111111111114</v>
+      </c>
+      <c r="C235" t="s">
+        <v>10</v>
+      </c>
+      <c r="D235">
+        <v>8</v>
+      </c>
+      <c r="E235" t="s">
+        <v>8</v>
+      </c>
+      <c r="F235" t="s">
+        <v>9</v>
+      </c>
+      <c r="G235" s="3" t="str">
+        <f>IF(OR(E235="Yes", F235="YES"), "YES", "NO")</f>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A236" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B236" s="9">
+        <v>0.67638888888888893</v>
+      </c>
+      <c r="C236" t="s">
+        <v>7</v>
+      </c>
+      <c r="D236">
+        <v>8</v>
+      </c>
+      <c r="E236" t="s">
+        <v>8</v>
+      </c>
+      <c r="F236" t="s">
+        <v>9</v>
+      </c>
+      <c r="G236" s="3" t="str">
+        <f>IF(OR(E236="Yes", F236="YES"), "YES", "NO")</f>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A237" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B237" s="9">
+        <v>0.6972222222222223</v>
+      </c>
+      <c r="C237" t="s">
+        <v>7</v>
+      </c>
+      <c r="D237">
+        <v>8</v>
+      </c>
+      <c r="E237" t="s">
+        <v>8</v>
+      </c>
+      <c r="F237" t="s">
+        <v>9</v>
+      </c>
+      <c r="G237" s="3" t="str">
+        <f>IF(OR(E237="Yes", F237="YES"), "YES", "NO")</f>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A238" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B238" s="9">
+        <v>0.76041666666666663</v>
+      </c>
+      <c r="C238" t="s">
+        <v>10</v>
+      </c>
+      <c r="D238">
+        <v>8</v>
+      </c>
+      <c r="E238" t="s">
+        <v>8</v>
+      </c>
+      <c r="F238" t="s">
+        <v>8</v>
+      </c>
+      <c r="G238" s="3" t="str">
+        <f>IF(OR(E238="Yes", F238="YES"), "YES", "NO")</f>
+        <v>YES</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A239" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B239" s="9">
+        <v>0.79305555555555562</v>
+      </c>
+      <c r="C239" t="s">
+        <v>7</v>
+      </c>
+      <c r="D239">
+        <v>8</v>
+      </c>
+      <c r="E239" t="s">
+        <v>9</v>
+      </c>
+      <c r="F239" t="s">
+        <v>9</v>
+      </c>
+      <c r="G239" s="3" t="str">
+        <f>IF(OR(E239="Yes", F239="YES"), "YES", "NO")</f>
+        <v>NO</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A240" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B240" s="9">
+        <v>0.84027777777777779</v>
+      </c>
+      <c r="C240" t="s">
+        <v>7</v>
+      </c>
+      <c r="D240">
+        <v>8</v>
+      </c>
+      <c r="E240" t="s">
+        <v>9</v>
+      </c>
+      <c r="F240" t="s">
+        <v>9</v>
+      </c>
+      <c r="G240" s="3" t="str">
+        <f>IF(OR(E240="Yes", F240="YES"), "YES", "NO")</f>
+        <v>NO</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G110">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="7" priority="10">
       <formula>G2="YES"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G110">
+    <cfRule type="expression" dxfId="6" priority="9">
+      <formula>G2="NO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G111:G152">
+    <cfRule type="expression" dxfId="5" priority="8">
+      <formula>G111="YES"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G111:G152">
+    <cfRule type="expression" dxfId="4" priority="7">
+      <formula>G111="NO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G153:G181">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>G153="YES"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G153:G181">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>G153="NO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G182:G240">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>G182="YES"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G182:G240">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>G2="NO"</formula>
+      <formula>G182="NO"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
